--- a/src/main/resources/espacios/Software/0 - SQL.xlsx
+++ b/src/main/resources/espacios/Software/0 - SQL.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="311">
   <si>
     <t xml:space="preserve">To understand SQL, it's helpful to know some basic concepts related to the structure and functioning of databases. Below is an explanation of the most important terms:</t>
   </si>
@@ -1262,6 +1262,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1274,6 +1275,7 @@
       <sz val="10"/>
       <name val="Liberation Mono;Courier New;DejaVu Sans Mono"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1318,32 +1320,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1370,9 +1376,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1857240</xdr:colOff>
+      <xdr:colOff>1855800</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1171080</xdr:rowOff>
+      <xdr:rowOff>1169640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1385,8 +1391,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="627840"/>
-          <a:ext cx="1857240" cy="1171080"/>
+          <a:off x="25518240" y="627840"/>
+          <a:ext cx="1855800" cy="1169640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1408,9 +1414,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2609640</xdr:colOff>
+      <xdr:colOff>2608200</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>466200</xdr:rowOff>
+      <xdr:rowOff>464760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1423,8 +1429,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="1986120"/>
-          <a:ext cx="2609640" cy="466200"/>
+          <a:off x="25518240" y="1986120"/>
+          <a:ext cx="2608200" cy="464760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1446,9 +1452,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2034000</xdr:colOff>
+      <xdr:colOff>2032560</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>533520</xdr:rowOff>
+      <xdr:rowOff>532080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1461,8 +1467,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="2602080"/>
-          <a:ext cx="2034000" cy="533520"/>
+          <a:off x="25518240" y="2602080"/>
+          <a:ext cx="2032560" cy="532080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1479,14 +1485,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>283680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4286160</xdr:colOff>
+      <xdr:colOff>4284720</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>656640</xdr:rowOff>
+      <xdr:rowOff>635760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1499,8 +1505,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="3695760"/>
-          <a:ext cx="4286160" cy="656640"/>
+          <a:off x="25518240" y="3695400"/>
+          <a:ext cx="4284720" cy="655200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1517,14 +1523,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>640440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4981680</xdr:colOff>
+      <xdr:colOff>4980240</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>628200</xdr:rowOff>
+      <xdr:rowOff>588600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1537,8 +1543,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="4374360"/>
-          <a:ext cx="4981680" cy="628200"/>
+          <a:off x="25518240" y="4355280"/>
+          <a:ext cx="4980240" cy="626760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1555,14 +1561,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>594000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3686040</xdr:colOff>
+      <xdr:colOff>3684600</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>637560</xdr:rowOff>
+      <xdr:rowOff>598320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1575,8 +1581,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="5006520"/>
-          <a:ext cx="3686040" cy="637560"/>
+          <a:off x="25518240" y="4987440"/>
+          <a:ext cx="3684600" cy="636120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1593,14 +1599,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>625320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3003480</xdr:colOff>
+      <xdr:colOff>3002040</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>712800</xdr:rowOff>
+      <xdr:rowOff>673560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1613,8 +1619,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="5669280"/>
-          <a:ext cx="3003480" cy="712800"/>
+          <a:off x="25518240" y="5650560"/>
+          <a:ext cx="3002040" cy="711360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1631,14 +1637,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>124920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2752560</xdr:colOff>
+      <xdr:colOff>2751120</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>628200</xdr:rowOff>
+      <xdr:rowOff>588960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1651,8 +1657,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="6863040"/>
-          <a:ext cx="2752560" cy="628200"/>
+          <a:off x="25518240" y="6844320"/>
+          <a:ext cx="2751120" cy="626760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1669,14 +1675,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>909360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3076560</xdr:colOff>
+      <xdr:colOff>3075120</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>570960</xdr:rowOff>
+      <xdr:rowOff>531360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1689,8 +1695,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="7810560"/>
-          <a:ext cx="3076560" cy="570960"/>
+          <a:off x="25518240" y="7791480"/>
+          <a:ext cx="3075120" cy="569520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1707,18 +1713,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>492120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1342800</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>495000</xdr:rowOff>
+      <xdr:colOff>3313080</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>331200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Image 10" descr=""/>
+        <xdr:cNvPr id="9" name="Image 13" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1727,8 +1733,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="8893800"/>
-          <a:ext cx="1342800" cy="495000"/>
+          <a:off x="25518240" y="12790080"/>
+          <a:ext cx="3313080" cy="426600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1745,18 +1751,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>390960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1342800</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>656640</xdr:rowOff>
+      <xdr:colOff>1989000</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>426600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Image 11" descr=""/>
+        <xdr:cNvPr id="10" name="Image 14" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1765,8 +1771,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="9540720"/>
-          <a:ext cx="1342800" cy="656640"/>
+          <a:off x="25518240" y="13276440"/>
+          <a:ext cx="1989000" cy="541080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1783,18 +1789,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>305280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1752480</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>609120</xdr:rowOff>
+      <xdr:colOff>4713480</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>769320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 12" descr=""/>
+        <xdr:cNvPr id="11" name="Image 15" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1803,8 +1809,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="10346040"/>
-          <a:ext cx="1752480" cy="609120"/>
+          <a:off x="25518240" y="15486840"/>
+          <a:ext cx="4713480" cy="921960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1821,18 +1827,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>794880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3314520</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>428040</xdr:rowOff>
+      <xdr:colOff>4799160</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>798120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Image 13" descr=""/>
+        <xdr:cNvPr id="12" name="Image 16" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1841,8 +1847,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="12828240"/>
-          <a:ext cx="3314520" cy="428040"/>
+          <a:off x="25518240" y="16434360"/>
+          <a:ext cx="4799160" cy="950760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1859,18 +1865,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>921240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1990440</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>542520</xdr:rowOff>
+      <xdr:colOff>5009040</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>969840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Image 14" descr=""/>
+        <xdr:cNvPr id="13" name="Image 17" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1879,8 +1885,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="13333680"/>
-          <a:ext cx="1990440" cy="542520"/>
+          <a:off x="25518240" y="17508240"/>
+          <a:ext cx="5009040" cy="1122120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1897,18 +1903,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1206000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4714920</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>923400</xdr:rowOff>
+      <xdr:colOff>4580280</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>674640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Image 15" descr=""/>
+        <xdr:cNvPr id="14" name="Image 18" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1917,8 +1923,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="15582240"/>
-          <a:ext cx="4714920" cy="923400"/>
+          <a:off x="25518240" y="18866520"/>
+          <a:ext cx="4580280" cy="826920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1935,18 +1941,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>447840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4800600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>952200</xdr:rowOff>
+      <xdr:colOff>3713400</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>807840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Image 16" descr=""/>
+        <xdr:cNvPr id="15" name="Image 19" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1955,8 +1961,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="16529760"/>
-          <a:ext cx="4800600" cy="952200"/>
+          <a:off x="25518240" y="20572200"/>
+          <a:ext cx="3713400" cy="960120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1973,18 +1979,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1000080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5010480</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>1123560</xdr:rowOff>
+      <xdr:colOff>4894560</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>769320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Image 17" descr=""/>
+        <xdr:cNvPr id="16" name="Image 20" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1993,8 +1999,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="17603640"/>
-          <a:ext cx="5010480" cy="1123560"/>
+          <a:off x="25518240" y="21724560"/>
+          <a:ext cx="4894560" cy="921960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2011,18 +2017,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>292680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4581720</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>828360</xdr:rowOff>
+      <xdr:colOff>4685040</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>674640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Image 18" descr=""/>
+        <xdr:cNvPr id="17" name="Image 21" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2031,8 +2037,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="18961560"/>
-          <a:ext cx="4581720" cy="828360"/>
+          <a:off x="25518240" y="23195880"/>
+          <a:ext cx="4685040" cy="826920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2049,18 +2055,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>254160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3714840</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>961560</xdr:rowOff>
+      <xdr:colOff>3999240</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>455040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Image 19" descr=""/>
+        <xdr:cNvPr id="18" name="Image 22" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2069,8 +2075,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="20667240"/>
-          <a:ext cx="3714840" cy="961560"/>
+          <a:off x="25518240" y="24613560"/>
+          <a:ext cx="3999240" cy="645840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2087,18 +2093,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>722160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4896000</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>923400</xdr:rowOff>
+      <xdr:colOff>2246400</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>331560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Image 20" descr=""/>
+        <xdr:cNvPr id="19" name="Image 23" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2107,8 +2113,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="21819960"/>
-          <a:ext cx="4896000" cy="923400"/>
+          <a:off x="25518240" y="25526520"/>
+          <a:ext cx="2246400" cy="541080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2125,18 +2131,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>642960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4686480</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>828360</xdr:rowOff>
+      <xdr:colOff>3942000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>826560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Image 21" descr=""/>
+        <xdr:cNvPr id="20" name="Image 24" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2145,8 +2151,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="23291280"/>
-          <a:ext cx="4686480" cy="828360"/>
+          <a:off x="25518240" y="26379000"/>
+          <a:ext cx="3942000" cy="1036440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2163,18 +2169,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1164240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4000680</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>647280</xdr:rowOff>
+      <xdr:colOff>3417840</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>931320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Image 22" descr=""/>
+        <xdr:cNvPr id="21" name="Image 25" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2183,8 +2189,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="24728040"/>
-          <a:ext cx="4000680" cy="647280"/>
+          <a:off x="25518240" y="27753120"/>
+          <a:ext cx="3417840" cy="1141200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2201,18 +2207,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>235800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2247840</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>542520</xdr:rowOff>
+      <xdr:colOff>5131080</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>1016640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Image 23" descr=""/>
+        <xdr:cNvPr id="22" name="Image 26" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2221,8 +2227,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="25659720"/>
-          <a:ext cx="2247840" cy="542520"/>
+          <a:off x="25518240" y="29730240"/>
+          <a:ext cx="5131080" cy="1226160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2239,18 +2245,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>216720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3943440</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>1037880</xdr:rowOff>
+      <xdr:colOff>4551480</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>474480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Image 24" descr=""/>
+        <xdr:cNvPr id="23" name="Image 27" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2259,8 +2265,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="26512560"/>
-          <a:ext cx="3943440" cy="1037880"/>
+          <a:off x="25518240" y="31861800"/>
+          <a:ext cx="4551480" cy="703080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2277,18 +2283,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>621000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3419280</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>1142640</xdr:rowOff>
+      <xdr:colOff>4160880</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>522000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Image 25" descr=""/>
+        <xdr:cNvPr id="24" name="Image 28" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2297,8 +2303,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="27886680"/>
-          <a:ext cx="3419280" cy="1142640"/>
+          <a:off x="25518240" y="32711400"/>
+          <a:ext cx="4160880" cy="769680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2315,18 +2321,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>621000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5132520</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>1227600</xdr:rowOff>
+      <xdr:colOff>2131920</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>493560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Image 26" descr=""/>
+        <xdr:cNvPr id="25" name="Image 29" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2335,8 +2341,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="29863440"/>
-          <a:ext cx="5132520" cy="1227600"/>
+          <a:off x="25518240" y="33580080"/>
+          <a:ext cx="2131920" cy="741240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2353,18 +2359,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>210240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4552920</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>704520</xdr:rowOff>
+      <xdr:colOff>3732480</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>779040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Image 27" descr=""/>
+        <xdr:cNvPr id="26" name="Image 30" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2373,8 +2379,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="32014080"/>
-          <a:ext cx="4552920" cy="704520"/>
+          <a:off x="25518240" y="35163720"/>
+          <a:ext cx="3732480" cy="1026720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2391,18 +2397,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>984240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4162320</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>771120</xdr:rowOff>
+      <xdr:colOff>3703680</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>703080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Image 28" descr=""/>
+        <xdr:cNvPr id="27" name="Image 31" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2411,8 +2417,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="32882760"/>
-          <a:ext cx="4162320" cy="771120"/>
+          <a:off x="25518240" y="36395640"/>
+          <a:ext cx="3703680" cy="950760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2429,18 +2435,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>652320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2133360</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>742680</xdr:rowOff>
+      <xdr:colOff>3618000</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>646200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Image 29" descr=""/>
+        <xdr:cNvPr id="28" name="Image 32" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2449,8 +2455,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="33751440"/>
-          <a:ext cx="2133360" cy="742680"/>
+          <a:off x="25518240" y="37295640"/>
+          <a:ext cx="3618000" cy="893520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2467,18 +2473,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>763560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3733920</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>1028160</xdr:rowOff>
+      <xdr:colOff>3560760</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>512280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Image 30" descr=""/>
+        <xdr:cNvPr id="29" name="Image 33" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2487,8 +2493,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="35335080"/>
-          <a:ext cx="3733920" cy="1028160"/>
+          <a:off x="25518240" y="38306520"/>
+          <a:ext cx="3560760" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2505,18 +2511,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>197640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3705120</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>52200</xdr:rowOff>
+      <xdr:colOff>4894560</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>474480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Image 31" descr=""/>
+        <xdr:cNvPr id="30" name="Image 34" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2525,8 +2531,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="36567000"/>
-          <a:ext cx="3705120" cy="952200"/>
+          <a:off x="25518240" y="39667320"/>
+          <a:ext cx="4894560" cy="722160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2543,18 +2549,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>537840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3619440</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>894960</xdr:rowOff>
+      <xdr:colOff>4446720</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>407160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Image 32" descr=""/>
+        <xdr:cNvPr id="31" name="Image 35" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2563,8 +2569,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="37467000"/>
-          <a:ext cx="3619440" cy="894960"/>
+          <a:off x="25518240" y="40452840"/>
+          <a:ext cx="4446720" cy="674280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2581,18 +2587,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>618120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3562200</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>761400</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>198000</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>484200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Image 33" descr=""/>
+        <xdr:cNvPr id="32" name="Image 36" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2601,8 +2607,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="38477880"/>
-          <a:ext cx="3562200" cy="761400"/>
+          <a:off x="25518240" y="41338080"/>
+          <a:ext cx="5542200" cy="750600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2618,19 +2624,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>72000</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>126720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4896000</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>723600</xdr:rowOff>
+      <xdr:colOff>1413360</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>457560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Image 34" descr=""/>
+        <xdr:cNvPr id="33" name="Image 10" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2639,8 +2645,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="39838680"/>
-          <a:ext cx="4896000" cy="723600"/>
+          <a:off x="25590240" y="8876880"/>
+          <a:ext cx="1341360" cy="493560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2656,19 +2662,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>72000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>606240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4448160</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>675720</xdr:rowOff>
+      <xdr:colOff>1413360</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>614520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Image 35" descr=""/>
+        <xdr:cNvPr id="34" name="Image 11" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2677,8 +2683,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="40643640"/>
-          <a:ext cx="4448160" cy="675720"/>
+          <a:off x="25590240" y="9519120"/>
+          <a:ext cx="1341360" cy="655200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2694,19 +2700,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>72000</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>762120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>199440</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>752040</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1823040</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>564480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Image 36" descr=""/>
+        <xdr:cNvPr id="35" name="Image 12" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2715,8 +2721,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25518600" y="41528520"/>
-          <a:ext cx="5543640" cy="752040"/>
+          <a:off x="25590240" y="10321920"/>
+          <a:ext cx="1751040" cy="607680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2738,18 +2744,18 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>523800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2666880</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1190160</xdr:rowOff>
+      <xdr:colOff>3284640</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2179440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Image 37" descr=""/>
+        <xdr:cNvPr id="36" name="Image 46" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2758,8 +2764,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="3462480"/>
-          <a:ext cx="2666880" cy="1190160"/>
+          <a:off x="25387920" y="17120880"/>
+          <a:ext cx="3284640" cy="2255760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2775,19 +2781,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>69840</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>25560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2438280</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1209240</xdr:rowOff>
+      <xdr:colOff>2735280</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1214280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Image 38" descr=""/>
+        <xdr:cNvPr id="37" name="Image 37" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2796,8 +2802,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="4963320"/>
-          <a:ext cx="2438280" cy="1209240"/>
+          <a:off x="25457760" y="3526200"/>
+          <a:ext cx="2665440" cy="1188720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2813,19 +2819,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>70200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>32040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2171520</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1161720</xdr:rowOff>
+      <xdr:colOff>2507040</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1239840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Image 39" descr=""/>
+        <xdr:cNvPr id="38" name="Image 38" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2834,8 +2840,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="6289560"/>
-          <a:ext cx="2171520" cy="1161720"/>
+          <a:off x="25458120" y="5033160"/>
+          <a:ext cx="2436840" cy="1207800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2851,19 +2857,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>69840</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>35640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3124080</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>1266480</xdr:rowOff>
+      <xdr:colOff>2239920</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1195920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Image 40" descr=""/>
+        <xdr:cNvPr id="39" name="Image 39" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2872,8 +2878,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="7710840"/>
-          <a:ext cx="3124080" cy="1266480"/>
+          <a:off x="25457760" y="6363360"/>
+          <a:ext cx="2170080" cy="1160280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2889,19 +2895,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>69840</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3848040</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1190160</xdr:rowOff>
+      <xdr:colOff>3192480</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1305360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Image 41" descr=""/>
+        <xdr:cNvPr id="40" name="Image 40" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2910,8 +2916,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="10632600"/>
-          <a:ext cx="3848040" cy="1190160"/>
+          <a:off x="25457760" y="7789320"/>
+          <a:ext cx="3122640" cy="1265040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2927,19 +2933,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>70200</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5010480</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1218960</xdr:rowOff>
+      <xdr:colOff>3916800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1225080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="Image 42" descr=""/>
+        <xdr:cNvPr id="41" name="Image 41" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2948,8 +2954,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="12216240"/>
-          <a:ext cx="5010480" cy="1218960"/>
+          <a:off x="25458120" y="10706760"/>
+          <a:ext cx="3846600" cy="1188720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2965,19 +2971,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>69840</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3429000</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>485280</xdr:rowOff>
+      <xdr:colOff>5078880</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1256760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Image 43" descr=""/>
+        <xdr:cNvPr id="42" name="Image 42" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2986,8 +2992,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="14142600"/>
-          <a:ext cx="3429000" cy="485280"/>
+          <a:off x="25457760" y="12293640"/>
+          <a:ext cx="5009040" cy="1217520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3003,19 +3009,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>70200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>36000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3486240</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>532800</xdr:rowOff>
+      <xdr:colOff>3497760</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>519840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Image 44" descr=""/>
+        <xdr:cNvPr id="43" name="Image 43" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3024,8 +3030,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="15027120"/>
-          <a:ext cx="3486240" cy="532800"/>
+          <a:off x="25458120" y="14216760"/>
+          <a:ext cx="3427560" cy="483840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3041,19 +3047,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>69840</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>33120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3085920</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>570960</xdr:rowOff>
+      <xdr:colOff>3554640</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>564480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Image 45" descr=""/>
+        <xdr:cNvPr id="44" name="Image 44" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3062,8 +3068,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="15800760"/>
-          <a:ext cx="3085920" cy="570960"/>
+          <a:off x="25457760" y="15098400"/>
+          <a:ext cx="3484800" cy="531360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3079,19 +3085,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>69840</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3286080</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2257200</xdr:rowOff>
+      <xdr:colOff>3154320</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>598320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Image 46" descr=""/>
+        <xdr:cNvPr id="45" name="Image 45" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3100,8 +3106,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="17159040"/>
-          <a:ext cx="3286080" cy="2257200"/>
+          <a:off x="25457760" y="15867720"/>
+          <a:ext cx="3084480" cy="569520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3117,15 +3123,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>70200</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>33480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3352680</xdr:colOff>
+      <xdr:colOff>3421440</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>1066320</xdr:rowOff>
+      <xdr:rowOff>1098360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3138,8 +3144,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="20601360"/>
-          <a:ext cx="3352680" cy="1066320"/>
+          <a:off x="25458120" y="20692080"/>
+          <a:ext cx="3351240" cy="1064880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3155,15 +3161,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>70200</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3143160</xdr:colOff>
+      <xdr:colOff>3211920</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>570960</xdr:rowOff>
+      <xdr:rowOff>606960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3176,8 +3182,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="21912120"/>
-          <a:ext cx="3143160" cy="570960"/>
+          <a:off x="25458120" y="22006440"/>
+          <a:ext cx="3141720" cy="569520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3193,15 +3199,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>69840</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>32040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4238640</xdr:colOff>
+      <xdr:colOff>4307040</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>466200</xdr:rowOff>
+      <xdr:rowOff>496800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3214,8 +3220,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="24722280"/>
-          <a:ext cx="4238640" cy="466200"/>
+          <a:off x="25457760" y="24811560"/>
+          <a:ext cx="4237200" cy="464760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3231,15 +3237,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>70200</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>24480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4390920</xdr:colOff>
+      <xdr:colOff>4459680</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>628200</xdr:rowOff>
+      <xdr:rowOff>651240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3252,8 +3258,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="25290720"/>
-          <a:ext cx="4390920" cy="628200"/>
+          <a:off x="25458120" y="25372440"/>
+          <a:ext cx="4389480" cy="626760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3269,15 +3275,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>69840</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>12960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5391360</xdr:colOff>
+      <xdr:colOff>5459760</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>1571400</xdr:rowOff>
+      <xdr:rowOff>1582920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3290,8 +3296,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="29168640"/>
-          <a:ext cx="5391360" cy="1571400"/>
+          <a:off x="25457760" y="29315160"/>
+          <a:ext cx="5389920" cy="1569960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3307,15 +3313,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>70200</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>25560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5943960</xdr:colOff>
+      <xdr:colOff>6012720</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>1352160</xdr:rowOff>
+      <xdr:rowOff>1376280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3328,8 +3334,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25387920" y="31079520"/>
-          <a:ext cx="5943960" cy="1352160"/>
+          <a:off x="25458120" y="31238280"/>
+          <a:ext cx="5942520" cy="1350720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3461,7 +3467,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="137.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="155.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="75.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="75.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3471,6 +3477,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -3479,7 +3486,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3490,7 +3497,7 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3501,6 +3508,9 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="48.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -3509,13 +3519,19 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="50.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3525,15 +3541,18 @@
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3544,6 +3563,9 @@
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="49.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
@@ -3552,6 +3574,9 @@
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
@@ -3560,6 +3585,9 @@
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="68.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -3568,6 +3596,9 @@
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -3576,6 +3607,9 @@
       <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -3584,7 +3618,7 @@
       <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3595,6 +3629,9 @@
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
@@ -3603,6 +3640,9 @@
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -3611,6 +3651,9 @@
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="F17" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
@@ -3619,7 +3662,7 @@
       <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3630,6 +3673,9 @@
       <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F19" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="63.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
@@ -3638,6 +3684,9 @@
       <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -3646,6 +3695,9 @@
       <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="F21" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -3654,26 +3706,27 @@
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3684,6 +3737,9 @@
       <c r="B25" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="F25" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="48.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -3692,6 +3748,9 @@
       <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="F26" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
@@ -3700,6 +3759,9 @@
       <c r="B27" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="F27" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
@@ -3708,13 +3770,19 @@
       <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="F28" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>56</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3724,6 +3792,9 @@
       <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="F30" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="84.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
@@ -3732,6 +3803,9 @@
       <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="F31" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="106.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
@@ -3740,6 +3814,9 @@
       <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="F32" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="87.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
@@ -3748,13 +3825,19 @@
       <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="F33" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>65</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>66</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3764,13 +3847,19 @@
       <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="F35" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="80.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>70</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3780,6 +3869,9 @@
       <c r="B37" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="F37" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="79.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
@@ -3788,32 +3880,41 @@
       <c r="B38" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F38" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="73.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="F40" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>80</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="108.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3823,13 +3924,19 @@
       <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="F42" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="120.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>84</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3839,6 +3946,9 @@
       <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="F44" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="134.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
@@ -3847,6 +3957,9 @@
       <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="F45" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
@@ -3855,77 +3968,105 @@
       <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="F46" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="68.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="F47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="68.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="F48" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="75.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="F49" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="F50" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>99</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="F51" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="97" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="F52" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="70.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="F53" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="79.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="F54" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="72.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>107</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>108</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3935,37 +4076,52 @@
       <c r="B56" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="F56" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="63.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="F57" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="F58" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="65.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>116</v>
       </c>
+      <c r="F59" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>118</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3988,257 +4144,313 @@
   <dimension ref="A1:F97"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="149.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="141.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="89.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="149.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="141.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="89.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="201.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>123</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>125</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="118.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>127</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>128</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>130</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="111.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>131</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>132</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="113.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>134</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="69.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>135</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>136</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>137</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="111.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>140</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>141</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>142</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="115.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>145</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>146</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>147</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>148</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="60.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>150</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>152</v>
       </c>
+      <c r="F17" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>153</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>154</v>
       </c>
+      <c r="F18" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="190.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>155</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="F19" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>157</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>159</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="103.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>162</v>
       </c>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="70.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>163</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>164</v>
       </c>
+      <c r="F23" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="80.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="69.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>170</v>
       </c>
+      <c r="F26" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>171</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="55.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F27" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>174</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4248,15 +4460,18 @@
       <c r="B29" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F29" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>177</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4267,7 +4482,7 @@
       <c r="B31" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4278,7 +4493,7 @@
       <c r="B32" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4289,18 +4504,18 @@
       <c r="B33" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F33" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>185</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4311,6 +4526,9 @@
       <c r="B35" s="1" t="s">
         <v>188</v>
       </c>
+      <c r="F35" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
@@ -4319,7 +4537,7 @@
       <c r="B36" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4330,7 +4548,7 @@
       <c r="B37" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4341,56 +4559,60 @@
       <c r="B38" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F39" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="F39" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>200</v>
       </c>
+      <c r="F41" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="123.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="7" t="s">
         <v>201</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
         <v>203</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4401,6 +4623,9 @@
       <c r="B44" s="1" t="s">
         <v>206</v>
       </c>
+      <c r="F44" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
@@ -4409,26 +4634,29 @@
       <c r="B45" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F45" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F45" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>209</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F46" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>211</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4439,18 +4667,18 @@
       <c r="B48" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F48" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F48" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>215</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4461,24 +4689,30 @@
       <c r="B50" s="1" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F50" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>219</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F51" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F51" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>222</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4488,18 +4722,18 @@
       <c r="B53" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F53" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F53" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>225</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4510,48 +4744,51 @@
       <c r="B55" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F55" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F55" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>229</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F56" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F56" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>231</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F57" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>233</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F58" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F58" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>235</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4562,31 +4799,29 @@
       <c r="B60" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F60" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>239</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F61" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F61" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>241</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F62" s="0" t="s">
-        <v>4</v>
-      </c>
+      <c r="F62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
@@ -4595,6 +4830,9 @@
       <c r="B63" s="1" t="s">
         <v>244</v>
       </c>
+      <c r="F63" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
@@ -4603,7 +4841,7 @@
       <c r="B64" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4614,18 +4852,18 @@
       <c r="B65" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F65" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F65" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>249</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4636,15 +4874,18 @@
       <c r="B67" s="1" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F67" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>253</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4655,6 +4896,9 @@
       <c r="B69" s="1" t="s">
         <v>256</v>
       </c>
+      <c r="F69" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
@@ -4663,18 +4907,18 @@
       <c r="B70" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F70" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F70" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>259</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4685,16 +4929,19 @@
       <c r="B72" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F72" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F72" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>261</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>262</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4704,27 +4951,30 @@
       <c r="B74" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F74" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F74" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>265</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F75" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F75" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>267</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>268</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4734,7 +4984,7 @@
       <c r="B77" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4745,7 +4995,7 @@
       <c r="B78" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4756,37 +5006,40 @@
       <c r="B79" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F79" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F79" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>275</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F80" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>277</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F81" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F81" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>279</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4797,7 +5050,7 @@
       <c r="B83" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4808,7 +5061,7 @@
       <c r="B84" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4819,6 +5072,9 @@
       <c r="B85" s="1" t="s">
         <v>286</v>
       </c>
+      <c r="F85" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
@@ -4827,7 +5083,7 @@
       <c r="B86" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4838,7 +5094,7 @@
       <c r="B87" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4849,7 +5105,7 @@
       <c r="B88" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4860,7 +5116,7 @@
       <c r="B89" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4871,7 +5127,7 @@
       <c r="B90" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4882,7 +5138,7 @@
       <c r="B91" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4893,7 +5149,7 @@
       <c r="B92" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4904,7 +5160,7 @@
       <c r="B93" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4915,7 +5171,7 @@
       <c r="B94" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4926,7 +5182,7 @@
       <c r="B95" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4937,7 +5193,7 @@
       <c r="B96" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4948,7 +5204,7 @@
       <c r="B97" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/src/main/resources/espacios/Software/0 - SQL.xlsx
+++ b/src/main/resources/espacios/Software/0 - SQL.xlsx
@@ -1236,7 +1236,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1260,6 +1260,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -1273,6 +1281,7 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Liberation Mono;Courier New;DejaVu Sans Mono"/>
       <family val="3"/>
       <charset val="1"/>
@@ -1325,16 +1334,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1345,11 +1354,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1376,9 +1385,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1855800</xdr:colOff>
+      <xdr:colOff>1855440</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1169640</xdr:rowOff>
+      <xdr:rowOff>1169280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1392,7 +1401,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="627840"/>
-          <a:ext cx="1855800" cy="1169640"/>
+          <a:ext cx="1855440" cy="1169280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1414,9 +1423,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2608200</xdr:colOff>
+      <xdr:colOff>2607840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>464760</xdr:rowOff>
+      <xdr:rowOff>464400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1430,7 +1439,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="1986120"/>
-          <a:ext cx="2608200" cy="464760"/>
+          <a:ext cx="2607840" cy="464400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1452,9 +1461,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2032560</xdr:colOff>
+      <xdr:colOff>2032200</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>532080</xdr:rowOff>
+      <xdr:rowOff>531720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1468,7 +1477,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="2602080"/>
-          <a:ext cx="2032560" cy="532080"/>
+          <a:ext cx="2032200" cy="531720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1490,9 +1499,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4284720</xdr:colOff>
+      <xdr:colOff>4284360</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>635760</xdr:rowOff>
+      <xdr:rowOff>635400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1506,7 +1515,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="3695400"/>
-          <a:ext cx="4284720" cy="655200"/>
+          <a:ext cx="4284360" cy="654840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1528,9 +1537,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4980240</xdr:colOff>
+      <xdr:colOff>4979880</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>588600</xdr:rowOff>
+      <xdr:rowOff>588240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1544,7 +1553,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="4355280"/>
-          <a:ext cx="4980240" cy="626760"/>
+          <a:ext cx="4979880" cy="626400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1566,9 +1575,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3684600</xdr:colOff>
+      <xdr:colOff>3684240</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>598320</xdr:rowOff>
+      <xdr:rowOff>597960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1582,7 +1591,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="4987440"/>
-          <a:ext cx="3684600" cy="636120"/>
+          <a:ext cx="3684240" cy="635760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1604,9 +1613,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3002040</xdr:colOff>
+      <xdr:colOff>3001680</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>673560</xdr:rowOff>
+      <xdr:rowOff>673200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1620,7 +1629,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="5650560"/>
-          <a:ext cx="3002040" cy="711360"/>
+          <a:ext cx="3001680" cy="711000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1642,9 +1651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2751120</xdr:colOff>
+      <xdr:colOff>2750760</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>588960</xdr:rowOff>
+      <xdr:rowOff>588600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1658,7 +1667,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="6844320"/>
-          <a:ext cx="2751120" cy="626760"/>
+          <a:ext cx="2750760" cy="626400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1680,9 +1689,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3075120</xdr:colOff>
+      <xdr:colOff>3074760</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>531360</xdr:rowOff>
+      <xdr:rowOff>531000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1696,7 +1705,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="7791480"/>
-          <a:ext cx="3075120" cy="569520"/>
+          <a:ext cx="3074760" cy="569160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1718,9 +1727,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3313080</xdr:colOff>
+      <xdr:colOff>3312720</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>331200</xdr:rowOff>
+      <xdr:rowOff>330840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1734,7 +1743,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="12790080"/>
-          <a:ext cx="3313080" cy="426600"/>
+          <a:ext cx="3312720" cy="426240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1756,9 +1765,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1989000</xdr:colOff>
+      <xdr:colOff>1988640</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>426600</xdr:rowOff>
+      <xdr:rowOff>426240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1772,7 +1781,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="13276440"/>
-          <a:ext cx="1989000" cy="541080"/>
+          <a:ext cx="1988640" cy="540720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1794,9 +1803,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4713480</xdr:colOff>
+      <xdr:colOff>4713120</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>769320</xdr:rowOff>
+      <xdr:rowOff>768960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1810,7 +1819,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="15486840"/>
-          <a:ext cx="4713480" cy="921960"/>
+          <a:ext cx="4713120" cy="921600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1832,9 +1841,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4799160</xdr:colOff>
+      <xdr:colOff>4798800</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>798120</xdr:rowOff>
+      <xdr:rowOff>797760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1848,7 +1857,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="16434360"/>
-          <a:ext cx="4799160" cy="950760"/>
+          <a:ext cx="4798800" cy="950400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1870,9 +1879,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5009040</xdr:colOff>
+      <xdr:colOff>5008680</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>969840</xdr:rowOff>
+      <xdr:rowOff>969480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1886,7 +1895,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="17508240"/>
-          <a:ext cx="5009040" cy="1122120"/>
+          <a:ext cx="5008680" cy="1121760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1908,9 +1917,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4580280</xdr:colOff>
+      <xdr:colOff>4579920</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>674640</xdr:rowOff>
+      <xdr:rowOff>674280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1924,7 +1933,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="18866520"/>
-          <a:ext cx="4580280" cy="826920"/>
+          <a:ext cx="4579920" cy="826560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1946,9 +1955,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3713400</xdr:colOff>
+      <xdr:colOff>3713040</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>807840</xdr:rowOff>
+      <xdr:rowOff>807480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1962,7 +1971,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="20572200"/>
-          <a:ext cx="3713400" cy="960120"/>
+          <a:ext cx="3713040" cy="959760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1984,9 +1993,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4894560</xdr:colOff>
+      <xdr:colOff>4894200</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>769320</xdr:rowOff>
+      <xdr:rowOff>768960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2000,7 +2009,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="21724560"/>
-          <a:ext cx="4894560" cy="921960"/>
+          <a:ext cx="4894200" cy="921600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2022,9 +2031,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4685040</xdr:colOff>
+      <xdr:colOff>4684680</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>674640</xdr:rowOff>
+      <xdr:rowOff>674280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2038,7 +2047,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="23195880"/>
-          <a:ext cx="4685040" cy="826920"/>
+          <a:ext cx="4684680" cy="826560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2060,9 +2069,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3999240</xdr:colOff>
+      <xdr:colOff>3998880</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>455040</xdr:rowOff>
+      <xdr:rowOff>454680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2076,7 +2085,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="24613560"/>
-          <a:ext cx="3999240" cy="645840"/>
+          <a:ext cx="3998880" cy="645480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2098,9 +2107,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2246400</xdr:colOff>
+      <xdr:colOff>2246040</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>331560</xdr:rowOff>
+      <xdr:rowOff>331200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2114,7 +2123,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="25526520"/>
-          <a:ext cx="2246400" cy="541080"/>
+          <a:ext cx="2246040" cy="540720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2136,9 +2145,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3942000</xdr:colOff>
+      <xdr:colOff>3941640</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>826560</xdr:rowOff>
+      <xdr:rowOff>826200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2152,7 +2161,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="26379000"/>
-          <a:ext cx="3942000" cy="1036440"/>
+          <a:ext cx="3941640" cy="1036080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2174,9 +2183,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3417840</xdr:colOff>
+      <xdr:colOff>3417480</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>931320</xdr:rowOff>
+      <xdr:rowOff>930960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2190,7 +2199,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="27753120"/>
-          <a:ext cx="3417840" cy="1141200"/>
+          <a:ext cx="3417480" cy="1140840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2212,9 +2221,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5131080</xdr:colOff>
+      <xdr:colOff>5130720</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>1016640</xdr:rowOff>
+      <xdr:rowOff>1016280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2228,7 +2237,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="29730240"/>
-          <a:ext cx="5131080" cy="1226160"/>
+          <a:ext cx="5130720" cy="1225800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2250,9 +2259,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4551480</xdr:colOff>
+      <xdr:colOff>4551120</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>474480</xdr:rowOff>
+      <xdr:rowOff>474120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2266,7 +2275,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="31861800"/>
-          <a:ext cx="4551480" cy="703080"/>
+          <a:ext cx="4551120" cy="702720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2288,9 +2297,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4160880</xdr:colOff>
+      <xdr:colOff>4160520</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>522000</xdr:rowOff>
+      <xdr:rowOff>521640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2304,7 +2313,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="32711400"/>
-          <a:ext cx="4160880" cy="769680"/>
+          <a:ext cx="4160520" cy="769320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2326,9 +2335,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2131920</xdr:colOff>
+      <xdr:colOff>2131560</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>493560</xdr:rowOff>
+      <xdr:rowOff>493200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2342,7 +2351,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="33580080"/>
-          <a:ext cx="2131920" cy="741240"/>
+          <a:ext cx="2131560" cy="740880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2364,9 +2373,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3732480</xdr:colOff>
+      <xdr:colOff>3732120</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>779040</xdr:rowOff>
+      <xdr:rowOff>778680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2380,7 +2389,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="35163720"/>
-          <a:ext cx="3732480" cy="1026720"/>
+          <a:ext cx="3732120" cy="1026360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2402,9 +2411,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3703680</xdr:colOff>
+      <xdr:colOff>3703320</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>703080</xdr:rowOff>
+      <xdr:rowOff>702720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2418,7 +2427,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="36395640"/>
-          <a:ext cx="3703680" cy="950760"/>
+          <a:ext cx="3703320" cy="950400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2440,9 +2449,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3618000</xdr:colOff>
+      <xdr:colOff>3617640</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>646200</xdr:rowOff>
+      <xdr:rowOff>645840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2456,7 +2465,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="37295640"/>
-          <a:ext cx="3618000" cy="893520"/>
+          <a:ext cx="3617640" cy="893160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2478,9 +2487,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3560760</xdr:colOff>
+      <xdr:colOff>3560400</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>512280</xdr:rowOff>
+      <xdr:rowOff>511920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2494,7 +2503,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="38306520"/>
-          <a:ext cx="3560760" cy="759960"/>
+          <a:ext cx="3560400" cy="759600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2516,9 +2525,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4894560</xdr:colOff>
+      <xdr:colOff>4894200</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>474480</xdr:rowOff>
+      <xdr:rowOff>474120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2532,7 +2541,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="39667320"/>
-          <a:ext cx="4894560" cy="722160"/>
+          <a:ext cx="4894200" cy="721800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2554,9 +2563,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4446720</xdr:colOff>
+      <xdr:colOff>4446360</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>407160</xdr:rowOff>
+      <xdr:rowOff>406800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2570,7 +2579,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="40452840"/>
-          <a:ext cx="4446720" cy="674280"/>
+          <a:ext cx="4446360" cy="673920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2592,9 +2601,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>198000</xdr:colOff>
+      <xdr:colOff>197640</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>484200</xdr:rowOff>
+      <xdr:rowOff>483840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2608,7 +2617,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25518240" y="41338080"/>
-          <a:ext cx="5542200" cy="750600"/>
+          <a:ext cx="5541840" cy="750240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2630,9 +2639,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1413360</xdr:colOff>
+      <xdr:colOff>1413000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>457560</xdr:rowOff>
+      <xdr:rowOff>457200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2646,7 +2655,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25590240" y="8876880"/>
-          <a:ext cx="1341360" cy="493560"/>
+          <a:ext cx="1341000" cy="493200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2668,9 +2677,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1413360</xdr:colOff>
+      <xdr:colOff>1413000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>614520</xdr:rowOff>
+      <xdr:rowOff>614160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2684,7 +2693,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25590240" y="9519120"/>
-          <a:ext cx="1341360" cy="655200"/>
+          <a:ext cx="1341000" cy="654840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2706,9 +2715,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1823040</xdr:colOff>
+      <xdr:colOff>1822680</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>564480</xdr:rowOff>
+      <xdr:rowOff>564120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2722,7 +2731,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25590240" y="10321920"/>
-          <a:ext cx="1751040" cy="607680"/>
+          <a:ext cx="1750680" cy="607320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2749,9 +2758,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3284640</xdr:colOff>
+      <xdr:colOff>3284280</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>2179440</xdr:rowOff>
+      <xdr:rowOff>2179080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2765,7 +2774,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25387920" y="17120880"/>
-          <a:ext cx="3284640" cy="2255760"/>
+          <a:ext cx="3284280" cy="2255400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2787,9 +2796,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2735280</xdr:colOff>
+      <xdr:colOff>2734920</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1214280</xdr:rowOff>
+      <xdr:rowOff>1213920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2803,7 +2812,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="3526200"/>
-          <a:ext cx="2665440" cy="1188720"/>
+          <a:ext cx="2665080" cy="1188360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2825,9 +2834,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2507040</xdr:colOff>
+      <xdr:colOff>2506680</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1239840</xdr:rowOff>
+      <xdr:rowOff>1239480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2841,7 +2850,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25458120" y="5033160"/>
-          <a:ext cx="2436840" cy="1207800"/>
+          <a:ext cx="2436480" cy="1207440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2863,9 +2872,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2239920</xdr:colOff>
+      <xdr:colOff>2239560</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>1195920</xdr:rowOff>
+      <xdr:rowOff>1195560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2879,7 +2888,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="6363360"/>
-          <a:ext cx="2170080" cy="1160280"/>
+          <a:ext cx="2169720" cy="1159920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2901,9 +2910,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3192480</xdr:colOff>
+      <xdr:colOff>3192120</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>1305360</xdr:rowOff>
+      <xdr:rowOff>1305000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2917,7 +2926,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="7789320"/>
-          <a:ext cx="3122640" cy="1265040"/>
+          <a:ext cx="3122280" cy="1264680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2939,9 +2948,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3916800</xdr:colOff>
+      <xdr:colOff>3916440</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>1225080</xdr:rowOff>
+      <xdr:rowOff>1224720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2955,7 +2964,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25458120" y="10706760"/>
-          <a:ext cx="3846600" cy="1188720"/>
+          <a:ext cx="3846240" cy="1188360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2977,9 +2986,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5078880</xdr:colOff>
+      <xdr:colOff>5078520</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>1256760</xdr:rowOff>
+      <xdr:rowOff>1256400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2993,7 +3002,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="12293640"/>
-          <a:ext cx="5009040" cy="1217520"/>
+          <a:ext cx="5008680" cy="1217160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3015,9 +3024,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3497760</xdr:colOff>
+      <xdr:colOff>3497400</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>519840</xdr:rowOff>
+      <xdr:rowOff>519480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3031,7 +3040,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25458120" y="14216760"/>
-          <a:ext cx="3427560" cy="483840"/>
+          <a:ext cx="3427200" cy="483480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3053,9 +3062,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3554640</xdr:colOff>
+      <xdr:colOff>3554280</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>564480</xdr:rowOff>
+      <xdr:rowOff>564120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3069,7 +3078,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="15098400"/>
-          <a:ext cx="3484800" cy="531360"/>
+          <a:ext cx="3484440" cy="531000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3091,9 +3100,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3154320</xdr:colOff>
+      <xdr:colOff>3153960</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>598320</xdr:rowOff>
+      <xdr:rowOff>597960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3107,7 +3116,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="15867720"/>
-          <a:ext cx="3084480" cy="569520"/>
+          <a:ext cx="3084120" cy="569160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3129,9 +3138,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3421440</xdr:colOff>
+      <xdr:colOff>3421080</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>1098360</xdr:rowOff>
+      <xdr:rowOff>1098000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3145,7 +3154,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25458120" y="20692080"/>
-          <a:ext cx="3351240" cy="1064880"/>
+          <a:ext cx="3350880" cy="1064520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3167,9 +3176,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3211920</xdr:colOff>
+      <xdr:colOff>3211560</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>606960</xdr:rowOff>
+      <xdr:rowOff>606600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3183,7 +3192,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25458120" y="22006440"/>
-          <a:ext cx="3141720" cy="569520"/>
+          <a:ext cx="3141360" cy="569160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3205,9 +3214,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4307040</xdr:colOff>
+      <xdr:colOff>4306680</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>496800</xdr:rowOff>
+      <xdr:rowOff>496440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3221,7 +3230,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="24811560"/>
-          <a:ext cx="4237200" cy="464760"/>
+          <a:ext cx="4236840" cy="464400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3243,9 +3252,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4459680</xdr:colOff>
+      <xdr:colOff>4459320</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>651240</xdr:rowOff>
+      <xdr:rowOff>650880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3259,7 +3268,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25458120" y="25372440"/>
-          <a:ext cx="4389480" cy="626760"/>
+          <a:ext cx="4389120" cy="626400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3281,9 +3290,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5459760</xdr:colOff>
+      <xdr:colOff>5459400</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>1582920</xdr:rowOff>
+      <xdr:rowOff>1582560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3297,7 +3306,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25457760" y="29315160"/>
-          <a:ext cx="5389920" cy="1569960"/>
+          <a:ext cx="5389560" cy="1569600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3319,9 +3328,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6012720</xdr:colOff>
+      <xdr:colOff>6012360</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>1376280</xdr:rowOff>
+      <xdr:rowOff>1375920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3335,7 +3344,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25458120" y="31238280"/>
-          <a:ext cx="5942520" cy="1350720"/>
+          <a:ext cx="5942160" cy="1350360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3467,7 +3476,9 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="137.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="155.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="75.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="3" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="75.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3477,7 +3488,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -3486,7 +3497,7 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3497,7 +3508,7 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3508,7 +3519,7 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3519,18 +3530,18 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="50.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3541,7 +3552,7 @@
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3552,7 +3563,7 @@
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3563,7 +3574,7 @@
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3574,7 +3585,7 @@
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3585,7 +3596,7 @@
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3596,7 +3607,7 @@
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3607,7 +3618,7 @@
       <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3618,7 +3629,7 @@
       <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3629,7 +3640,7 @@
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3640,7 +3651,7 @@
       <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3651,7 +3662,7 @@
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3662,7 +3673,7 @@
       <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3673,7 +3684,7 @@
       <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3684,7 +3695,7 @@
       <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3695,7 +3706,7 @@
       <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3706,7 +3717,7 @@
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="2"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
@@ -3715,7 +3726,7 @@
       <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3726,7 +3737,7 @@
       <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3737,7 +3748,7 @@
       <c r="B25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3748,7 +3759,7 @@
       <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3759,7 +3770,7 @@
       <c r="B27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3770,18 +3781,18 @@
       <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3792,7 +3803,7 @@
       <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3803,7 +3814,7 @@
       <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3814,7 +3825,7 @@
       <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3825,18 +3836,18 @@
       <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3847,18 +3858,18 @@
       <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="80.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3869,7 +3880,7 @@
       <c r="B37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3880,7 +3891,7 @@
       <c r="B38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3891,29 +3902,29 @@
       <c r="B39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="73.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3924,18 +3935,18 @@
       <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="120.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3946,7 +3957,7 @@
       <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3957,7 +3968,7 @@
       <c r="B45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3968,104 +3979,104 @@
       <c r="B46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="68.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F47" s="2"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="68.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="75.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="97" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="70.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="79.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="72.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4076,51 +4087,51 @@
       <c r="B56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="63.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="4" t="s">
         <v>113</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="65.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4144,50 +4155,52 @@
   <dimension ref="A1:F97"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="149.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="141.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="89.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="149.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="141.21"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="3" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="89.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4198,7 +4211,7 @@
       <c r="B5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4209,7 +4222,7 @@
       <c r="B6" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4220,7 +4233,7 @@
       <c r="B7" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4231,40 +4244,40 @@
       <c r="B8" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="69.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>135</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="111.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>139</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4275,29 +4288,29 @@
       <c r="B12" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="115.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>143</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>145</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4308,7 +4321,7 @@
       <c r="B15" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4319,29 +4332,29 @@
       <c r="B16" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>151</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>153</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4352,29 +4365,29 @@
       <c r="B19" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4385,7 +4398,7 @@
       <c r="B22" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F22" s="2"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="70.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
@@ -4394,29 +4407,29 @@
       <c r="B23" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="80.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>165</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="69.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>167</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4427,7 +4440,7 @@
       <c r="B26" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4438,7 +4451,7 @@
       <c r="B27" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4449,7 +4462,7 @@
       <c r="B28" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4460,7 +4473,7 @@
       <c r="B29" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4471,7 +4484,7 @@
       <c r="B30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4482,7 +4495,7 @@
       <c r="B31" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4493,7 +4506,7 @@
       <c r="B32" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4504,7 +4517,7 @@
       <c r="B33" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4515,7 +4528,7 @@
       <c r="B34" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4526,7 +4539,7 @@
       <c r="B35" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4537,7 +4550,7 @@
       <c r="B36" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4548,7 +4561,7 @@
       <c r="B37" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4559,40 +4572,40 @@
       <c r="B38" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>195</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4603,16 +4616,16 @@
       <c r="B42" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F42" s="2"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="1" t="s">
         <v>203</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4623,7 +4636,7 @@
       <c r="B44" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4634,7 +4647,7 @@
       <c r="B45" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4645,7 +4658,7 @@
       <c r="B46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4656,7 +4669,7 @@
       <c r="B47" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4667,7 +4680,7 @@
       <c r="B48" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4678,7 +4691,7 @@
       <c r="B49" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4689,7 +4702,7 @@
       <c r="B50" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4700,7 +4713,7 @@
       <c r="B51" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4711,7 +4724,7 @@
       <c r="B52" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4722,7 +4735,7 @@
       <c r="B53" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4733,7 +4746,7 @@
       <c r="B54" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4744,7 +4757,7 @@
       <c r="B55" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4755,7 +4768,7 @@
       <c r="B56" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4766,7 +4779,7 @@
       <c r="B57" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4777,7 +4790,7 @@
       <c r="B58" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4788,7 +4801,7 @@
       <c r="B59" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4799,7 +4812,7 @@
       <c r="B60" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4810,7 +4823,7 @@
       <c r="B61" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4821,7 +4834,7 @@
       <c r="B62" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F62" s="2"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
@@ -4830,7 +4843,7 @@
       <c r="B63" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4841,7 +4854,7 @@
       <c r="B64" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="F64" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4852,7 +4865,7 @@
       <c r="B65" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="F65" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4863,7 +4876,7 @@
       <c r="B66" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4874,7 +4887,7 @@
       <c r="B67" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F67" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4885,7 +4898,7 @@
       <c r="B68" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4896,7 +4909,7 @@
       <c r="B69" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4907,7 +4920,7 @@
       <c r="B70" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4918,7 +4931,7 @@
       <c r="B71" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="F71" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4929,7 +4942,7 @@
       <c r="B72" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4940,7 +4953,7 @@
       <c r="B73" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="F73" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4951,7 +4964,7 @@
       <c r="B74" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="F74" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4962,7 +4975,7 @@
       <c r="B75" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F75" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4973,7 +4986,7 @@
       <c r="B76" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4984,7 +4997,7 @@
       <c r="B77" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="F77" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4995,7 +5008,7 @@
       <c r="B78" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5006,7 +5019,7 @@
       <c r="B79" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="F79" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5017,7 +5030,7 @@
       <c r="B80" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F80" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5028,7 +5041,7 @@
       <c r="B81" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F81" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5039,7 +5052,7 @@
       <c r="B82" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5050,7 +5063,7 @@
       <c r="B83" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5061,7 +5074,7 @@
       <c r="B84" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F84" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5072,7 +5085,7 @@
       <c r="B85" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F85" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5083,7 +5096,7 @@
       <c r="B86" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F86" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5094,7 +5107,7 @@
       <c r="B87" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F87" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5105,7 +5118,7 @@
       <c r="B88" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F88" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5116,7 +5129,7 @@
       <c r="B89" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="F89" s="2" t="s">
+      <c r="F89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5127,7 +5140,7 @@
       <c r="B90" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F90" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5138,7 +5151,7 @@
       <c r="B91" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5149,7 +5162,7 @@
       <c r="B92" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F92" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5160,7 +5173,7 @@
       <c r="B93" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="F93" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5171,7 +5184,7 @@
       <c r="B94" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5182,7 +5195,7 @@
       <c r="B95" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="F95" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5193,7 +5206,7 @@
       <c r="B96" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F96" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5204,7 +5217,7 @@
       <c r="B97" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="F97" s="3" t="s">
         <v>4</v>
       </c>
     </row>
